--- a/results.xlsx
+++ b/results.xlsx
@@ -9,17 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2364" windowHeight="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2364" windowHeight="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Датасет 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Датасат 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="20">
   <si>
     <t>Сегментация по предложениям</t>
   </si>
@@ -76,6 +77,9 @@
   </si>
   <si>
     <t>50 на каждый (множественное размещение)</t>
+  </si>
+  <si>
+    <t>Бинарная классификация</t>
   </si>
 </sst>
 </file>
@@ -363,21 +367,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -405,6 +400,24 @@
     </xf>
     <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent" xfId="1"/>
@@ -703,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.44140625" customWidth="1"/>
@@ -712,9 +725,10 @@
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
     <col min="5" max="5" width="11.21875" customWidth="1"/>
     <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -728,248 +742,262 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="16"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="8"/>
+      <c r="K3" s="5"/>
       <c r="L3" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N3" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="4">
         <v>0.35399999999999998</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="4">
         <v>0.35699999999999998</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9">
+      <c r="E4" s="5"/>
+      <c r="F4" s="6">
         <v>0.39200000000000002</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="4">
         <v>0.379</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="5">
         <v>0.40300000000000002</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <v>0.40600000000000003</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="13">
         <v>0.435</v>
       </c>
-      <c r="K4" s="8"/>
+      <c r="K4" s="5"/>
       <c r="L4" s="2">
         <f>AVERAGE(C4:K4)</f>
         <v>0.3894285714285714</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="N4" s="19">
+        <v>0.44500000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>0.36399999999999999</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="4">
         <v>0.38100000000000001</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9">
+      <c r="E5" s="5"/>
+      <c r="F5" s="6">
         <v>0.38800000000000001</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="8">
         <v>0.40799999999999997</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="5">
         <v>0.40400000000000003</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="5">
         <v>0.36799999999999999</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="5">
         <v>0.39</v>
       </c>
-      <c r="K5" s="8"/>
+      <c r="K5" s="5"/>
       <c r="L5" s="2">
         <f t="shared" ref="L5:L8" si="0">AVERAGE(C5:K5)</f>
         <v>0.38614285714285712</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>0.29899999999999999</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="4">
         <v>0.39200000000000002</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9">
+      <c r="E6" s="5"/>
+      <c r="F6" s="6">
         <v>0.375</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="4">
         <v>0.39100000000000001</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="5">
         <v>0.39300000000000002</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="13">
         <v>0.42</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="5">
         <v>0.41799999999999998</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="5"/>
       <c r="L6" s="2">
         <f t="shared" si="0"/>
         <v>0.38400000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>0.434</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="4">
         <v>0.36499999999999999</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9">
+      <c r="E7" s="5"/>
+      <c r="F7" s="6">
         <v>0.375</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="4">
         <v>0.38100000000000001</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="5">
         <v>0.39800000000000002</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="5">
         <v>0.42799999999999999</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="5">
         <v>0.43</v>
       </c>
-      <c r="K7" s="8"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="2">
         <f t="shared" si="0"/>
         <v>0.40157142857142858</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <v>0.33200000000000002</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="4">
         <v>0.36499999999999999</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9">
+      <c r="E8" s="5"/>
+      <c r="F8" s="6">
         <v>0.29099999999999998</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="4">
         <v>0.313</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="5">
         <v>0.316</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="5">
         <v>0.318</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="5">
         <v>0.33800000000000002</v>
       </c>
-      <c r="K8" s="8"/>
+      <c r="K8" s="5"/>
       <c r="L8" s="2">
         <f t="shared" si="0"/>
         <v>0.32471428571428573</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N8" s="18">
+        <v>0.33200000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
       <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N9" s="17"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
       <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N10" s="17"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1009,7 +1037,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1023,7 +1051,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1037,7 +1065,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1051,48 +1079,48 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="5"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="16"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:13" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="10" t="s">
+      <c r="J16" s="5"/>
+      <c r="K16" s="7" t="s">
         <v>16</v>
       </c>
       <c r="L16" s="2"/>
@@ -1102,30 +1130,30 @@
     </row>
     <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="6">
         <v>0.34799999999999998</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="12">
+      <c r="D17" s="4"/>
+      <c r="E17" s="9">
         <v>0.373</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="9">
         <v>0.39900000000000002</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="4">
         <v>0.39900000000000002</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="8">
         <v>0.40200000000000002</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="9">
         <v>0.39900000000000002</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8">
+      <c r="J17" s="5"/>
+      <c r="K17" s="5">
         <f>AVERAGE(C17:I17)</f>
         <v>0.38666666666666671</v>
       </c>
@@ -1133,30 +1161,30 @@
     </row>
     <row r="18" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="6">
         <v>0.36499999999999999</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="12">
+      <c r="D18" s="4"/>
+      <c r="E18" s="9">
         <v>0.38100000000000001</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="9">
         <v>0.39300000000000002</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="4">
         <v>0.42199999999999999</v>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="8">
         <v>0.42299999999999999</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="9">
         <v>0.40600000000000003</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8">
+      <c r="J18" s="5"/>
+      <c r="K18" s="5">
         <f t="shared" ref="K18:K21" si="2">AVERAGE(C18:I18)</f>
         <v>0.39833333333333337</v>
       </c>
@@ -1164,30 +1192,30 @@
     </row>
     <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="6">
         <v>0.315</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="12">
+      <c r="D19" s="4"/>
+      <c r="E19" s="9">
         <v>0.372</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <v>0.42299999999999999</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="4">
         <v>0.41699999999999998</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="4">
         <v>0.41399999999999998</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="9">
         <v>0.40400000000000003</v>
       </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8">
+      <c r="J19" s="5"/>
+      <c r="K19" s="5">
         <f t="shared" si="2"/>
         <v>0.39083333333333337</v>
       </c>
@@ -1195,30 +1223,30 @@
     </row>
     <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="6">
         <v>0.33400000000000002</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="12">
+      <c r="D20" s="4"/>
+      <c r="E20" s="9">
         <v>0.371</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="9">
         <v>0.39400000000000002</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="4">
         <v>0.40300000000000002</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="8">
         <v>0.41</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="9">
         <v>0.40200000000000002</v>
       </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8">
+      <c r="J20" s="5"/>
+      <c r="K20" s="5">
         <f t="shared" si="2"/>
         <v>0.38566666666666666</v>
       </c>
@@ -1226,30 +1254,30 @@
     </row>
     <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="6">
         <v>0.33800000000000002</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="12">
+      <c r="D21" s="4"/>
+      <c r="E21" s="9">
         <v>0.29099999999999998</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="9">
         <v>0.36</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="4">
         <v>0.36499999999999999</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="4">
         <v>0.40200000000000002</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="9">
         <v>0.39</v>
       </c>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8">
+      <c r="J21" s="5"/>
+      <c r="K21" s="5">
         <f t="shared" si="2"/>
         <v>0.35766666666666674</v>
       </c>
@@ -1257,69 +1285,69 @@
     </row>
     <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="5">
         <f>AVERAGE(C17:C21)</f>
         <v>0.34</v>
       </c>
-      <c r="D24" s="8" t="e">
+      <c r="D24" s="5" t="e">
         <f t="shared" ref="D24:I24" si="3">AVERAGE(D17:D21)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="5">
         <f t="shared" si="3"/>
         <v>0.35759999999999997</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="5">
         <f t="shared" si="3"/>
         <v>0.39379999999999998</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="5">
         <f t="shared" si="3"/>
         <v>0.40120000000000006</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="5">
         <f t="shared" si="3"/>
         <v>0.41019999999999995</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="5">
         <f t="shared" si="3"/>
         <v>0.40020000000000006</v>
       </c>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -1339,7 +1367,7 @@
     <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="15"/>
+      <c r="C26" s="12"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -1365,9 +1393,10 @@
       <c r="L27" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B15:K15"/>
+    <mergeCell ref="N4:N7"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1376,4 +1405,538 @@
     <oddFooter>&amp;CСтраница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="14" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="2" t="e">
+        <f>AVERAGE(C4:K4)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="2" t="e">
+        <f t="shared" ref="L5:L8" si="0">AVERAGE(C5:K5)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="18"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="2"/>
+      <c r="N9" s="17"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="2"/>
+      <c r="N10" s="17"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="e">
+        <f>AVERAGE(C4:C8)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D11" s="2" t="e">
+        <f t="shared" ref="D11:J11" si="1">AVERAGE(D4:D8)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E11" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F11" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G11" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H11" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I11" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J11" s="2" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="5" t="e">
+        <f>AVERAGE(C17:C21)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D24" s="5" t="e">
+        <f t="shared" ref="D24:I24" si="2">AVERAGE(D17:D21)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E24" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F24" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G24" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H24" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I24" s="5" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="N4:N7"/>
+    <mergeCell ref="B15:K15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/results.xlsx
+++ b/results.xlsx
@@ -400,6 +400,12 @@
     </xf>
     <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -407,12 +413,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -744,18 +744,18 @@
     </row>
     <row r="2" spans="1:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="109.2" x14ac:dyDescent="0.3">
@@ -787,7 +787,7 @@
       <c r="L3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="15" t="s">
         <v>19</v>
       </c>
     </row>
@@ -961,7 +961,7 @@
         <f t="shared" si="0"/>
         <v>0.32471428571428573</v>
       </c>
-      <c r="N8" s="18">
+      <c r="N8" s="15">
         <v>0.33200000000000002</v>
       </c>
     </row>
@@ -978,7 +978,7 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="2"/>
-      <c r="N9" s="17"/>
+      <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
@@ -995,7 +995,7 @@
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="2"/>
-      <c r="N10" s="17"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
@@ -1081,18 +1081,18 @@
     </row>
     <row r="15" spans="1:14" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="18"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:14" ht="109.2" x14ac:dyDescent="0.3">
@@ -1368,7 +1368,6 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -1381,7 +1380,6 @@
     <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -1432,21 +1430,21 @@
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
@@ -1475,7 +1473,7 @@
       <c r="L3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="15" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1577,7 +1575,7 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -1592,7 +1590,7 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="2"/>
-      <c r="N9" s="17"/>
+      <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
@@ -1609,7 +1607,7 @@
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="2"/>
-      <c r="N10" s="17"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
@@ -1695,18 +1693,18 @@
     </row>
     <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="18"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:14" ht="93.6" x14ac:dyDescent="0.3">

--- a/results.xlsx
+++ b/results.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Датасет 1" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Датасат 2" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Датасет3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="36">
   <si>
     <t xml:space="preserve">Сегментация по предложениям</t>
   </si>
@@ -81,6 +82,54 @@
   </si>
   <si>
     <t xml:space="preserve">Среднее</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обзор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Цель </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.377</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.388</t>
   </si>
 </sst>
 </file>
@@ -413,76 +462,72 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -584,72 +629,72 @@
   <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="1"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="108.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="N3" s="6" t="s">
@@ -657,21 +702,21 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>0.354</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.357</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="n">
         <v>0.392</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="3" t="n">
         <v>0.379</v>
       </c>
       <c r="H4" s="5" t="n">
@@ -684,7 +729,7 @@
         <v>0.435</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="1" t="n">
+      <c r="L4" s="2" t="n">
         <f aca="false">AVERAGE(C4:K4)</f>
         <v>0.389428571428571</v>
       </c>
@@ -693,14 +738,14 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>0.364</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.381</v>
       </c>
       <c r="E5" s="5"/>
@@ -720,28 +765,28 @@
         <v>0.39</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="2" t="n">
         <f aca="false">AVERAGE(C5:K5)</f>
         <v>0.386142857142857</v>
       </c>
       <c r="N5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>0.299</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.392</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="7" t="n">
         <v>0.375</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="3" t="n">
         <v>0.391</v>
       </c>
       <c r="H6" s="5" t="n">
@@ -754,28 +799,28 @@
         <v>0.418</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="1" t="n">
+      <c r="L6" s="2" t="n">
         <f aca="false">AVERAGE(C6:K6)</f>
         <v>0.384</v>
       </c>
       <c r="N6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>0.434</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.365</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="7" t="n">
         <v>0.375</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="3" t="n">
         <v>0.381</v>
       </c>
       <c r="H7" s="5" t="n">
@@ -788,28 +833,28 @@
         <v>0.43</v>
       </c>
       <c r="K7" s="5"/>
-      <c r="L7" s="1" t="n">
+      <c r="L7" s="2" t="n">
         <f aca="false">AVERAGE(C7:K7)</f>
         <v>0.401571428571429</v>
       </c>
       <c r="N7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="3" t="n">
         <v>0.332</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="3" t="n">
         <v>0.365</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="7" t="n">
         <v>0.291</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="3" t="n">
         <v>0.313</v>
       </c>
       <c r="H8" s="5" t="n">
@@ -822,7 +867,7 @@
         <v>0.338</v>
       </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="1" t="n">
+      <c r="L8" s="2" t="n">
         <f aca="false">AVERAGE(C8:K8)</f>
         <v>0.324714285714286</v>
       </c>
@@ -831,184 +876,184 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
       <c r="E9" s="5"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="4"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="1"/>
+      <c r="L9" s="2"/>
       <c r="N9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
       <c r="E10" s="5"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="4"/>
+      <c r="G10" s="3"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-      <c r="L10" s="1"/>
+      <c r="L10" s="2"/>
       <c r="N10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <f aca="false">AVERAGE(C4:C8)</f>
         <v>0.3566</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="2" t="n">
         <f aca="false">AVERAGE(D4:D8)</f>
         <v>0.372</v>
       </c>
-      <c r="E11" s="1" t="e">
+      <c r="E11" s="2" t="e">
         <f aca="false">AVERAGE(E4:E8)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="2" t="n">
         <f aca="false">AVERAGE(F4:F8)</f>
         <v>0.3642</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="2" t="n">
         <f aca="false">AVERAGE(G4:G8)</f>
         <v>0.3744</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <f aca="false">AVERAGE(H4:H8)</f>
         <v>0.3828</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I11" s="2" t="n">
         <f aca="false">AVERAGE(I4:I8)</f>
         <v>0.388</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <f aca="false">AVERAGE(J4:J8)</f>
         <v>0.4022</v>
       </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="1"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="108.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4" t="s">
+      <c r="A16" s="2"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J16" s="5"/>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L16" s="1"/>
+      <c r="L16" s="2"/>
       <c r="M16" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>0.348</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="3"/>
       <c r="E17" s="13" t="n">
         <v>0.373</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>0.399</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="3" t="n">
         <v>0.399</v>
       </c>
       <c r="H17" s="10" t="n">
@@ -1022,24 +1067,24 @@
         <f aca="false">AVERAGE(C17:I17)</f>
         <v>0.386666666666667</v>
       </c>
-      <c r="L17" s="1"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>0.365</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="3"/>
       <c r="E18" s="13" t="n">
         <v>0.381</v>
       </c>
       <c r="F18" s="13" t="n">
         <v>0.393</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="3" t="n">
         <v>0.422</v>
       </c>
       <c r="H18" s="10" t="n">
@@ -1053,27 +1098,27 @@
         <f aca="false">AVERAGE(C18:I18)</f>
         <v>0.398333333333333</v>
       </c>
-      <c r="L18" s="1"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>0.315</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="3"/>
       <c r="E19" s="13" t="n">
         <v>0.372</v>
       </c>
       <c r="F19" s="14" t="n">
         <v>0.423</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="3" t="n">
         <v>0.417</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="3" t="n">
         <v>0.414</v>
       </c>
       <c r="I19" s="13" t="n">
@@ -1084,24 +1129,24 @@
         <f aca="false">AVERAGE(C19:I19)</f>
         <v>0.390833333333333</v>
       </c>
-      <c r="L19" s="1"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>0.334</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="3"/>
       <c r="E20" s="13" t="n">
         <v>0.371</v>
       </c>
       <c r="F20" s="13" t="n">
         <v>0.394</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="3" t="n">
         <v>0.403</v>
       </c>
       <c r="H20" s="10" t="n">
@@ -1115,27 +1160,27 @@
         <f aca="false">AVERAGE(C20:I20)</f>
         <v>0.385666666666667</v>
       </c>
-      <c r="L20" s="1"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1"/>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>0.338</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="3"/>
       <c r="E21" s="13" t="n">
         <v>0.291</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>0.36</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="3" t="n">
         <v>0.365</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="3" t="n">
         <v>0.402</v>
       </c>
       <c r="I21" s="13" t="n">
@@ -1146,41 +1191,41 @@
         <f aca="false">AVERAGE(C21:I21)</f>
         <v>0.357666666666667</v>
       </c>
-      <c r="L21" s="1"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
       <c r="I22" s="13"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
-      <c r="L22" s="1"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1"/>
-      <c r="B23" s="3" t="s">
+      <c r="A23" s="2"/>
+      <c r="B23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
       <c r="I23" s="13"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1"/>
-      <c r="B24" s="15" t="s">
+      <c r="A24" s="2"/>
+      <c r="B24" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C24" s="5" t="n">
@@ -1213,47 +1258,47 @@
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="1"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="16"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="15"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1279,67 +1324,67 @@
   <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="1" width="10.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="1"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="93" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="N3" s="6" t="s">
@@ -1347,17 +1392,17 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>0.385</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="3" t="n">
         <v>0.398</v>
       </c>
       <c r="H4" s="5" t="n">
@@ -1370,7 +1415,7 @@
         <v>0.414</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="17" t="n">
+      <c r="L4" s="16" t="n">
         <f aca="false">AVERAGE(C4:K4)</f>
         <v>0.4082</v>
       </c>
@@ -1379,17 +1424,17 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>0.381</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="3" t="n">
         <v>0.403</v>
       </c>
       <c r="H5" s="8" t="n">
@@ -1402,24 +1447,24 @@
         <v>0.386</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="2" t="n">
         <f aca="false">AVERAGE(C5:K5)</f>
         <v>0.393</v>
       </c>
       <c r="N5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="3" t="n">
         <v>0.366</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="5"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="3" t="n">
         <v>0.37</v>
       </c>
       <c r="H6" s="8" t="n">
@@ -1432,24 +1477,24 @@
         <v>0.373</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="1" t="n">
+      <c r="L6" s="2" t="n">
         <f aca="false">AVERAGE(C6:K6)</f>
         <v>0.3714</v>
       </c>
       <c r="N6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>0.419</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="5"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="3" t="n">
         <v>0.376</v>
       </c>
       <c r="H7" s="5" t="n">
@@ -1462,24 +1507,24 @@
         <v>0.394</v>
       </c>
       <c r="K7" s="5"/>
-      <c r="L7" s="1" t="n">
+      <c r="L7" s="2" t="n">
         <f aca="false">AVERAGE(C7:K7)</f>
         <v>0.3952</v>
       </c>
       <c r="N7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="3" t="n">
         <v>0.332</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="5"/>
       <c r="F8" s="7"/>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="3" t="n">
         <v>0.292</v>
       </c>
       <c r="H8" s="5" t="n">
@@ -1492,7 +1537,7 @@
         <v>0.33</v>
       </c>
       <c r="K8" s="5"/>
-      <c r="L8" s="1" t="n">
+      <c r="L8" s="2" t="n">
         <f aca="false">AVERAGE(C8:K8)</f>
         <v>0.3126</v>
       </c>
@@ -1501,291 +1546,291 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
       <c r="E9" s="5"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="4"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="1"/>
+      <c r="L9" s="2"/>
       <c r="N9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="2"/>
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
       <c r="E10" s="5"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="4"/>
+      <c r="G10" s="3"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-      <c r="L10" s="1"/>
+      <c r="L10" s="2"/>
       <c r="N10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <f aca="false">AVERAGE(C4:C8)</f>
         <v>0.3766</v>
       </c>
-      <c r="D11" s="1" t="e">
+      <c r="D11" s="2" t="e">
         <f aca="false">AVERAGE(D4:D8)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E11" s="1" t="e">
+      <c r="E11" s="2" t="e">
         <f aca="false">AVERAGE(E4:E8)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F11" s="1" t="e">
+      <c r="F11" s="2" t="e">
         <f aca="false">AVERAGE(F4:F8)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="2" t="n">
         <f aca="false">AVERAGE(G4:G8)</f>
         <v>0.3678</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <f aca="false">AVERAGE(H4:H8)</f>
         <v>0.3756</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I11" s="2" t="n">
         <f aca="false">AVERAGE(I4:I8)</f>
         <v>0.381</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <f aca="false">AVERAGE(J4:J8)</f>
         <v>0.3794</v>
       </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="1"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="93" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4" t="s">
+      <c r="A16" s="2"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="3" t="s">
         <v>6</v>
       </c>
       <c r="J16" s="5"/>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L16" s="1"/>
+      <c r="L16" s="2"/>
       <c r="M16" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="7"/>
-      <c r="D17" s="4"/>
+      <c r="D17" s="3"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4" t="n">
+      <c r="G17" s="3"/>
+      <c r="H17" s="3" t="n">
         <v>0.391</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
-      <c r="L17" s="1"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="4"/>
+      <c r="D18" s="3"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4" t="n">
+      <c r="G18" s="3"/>
+      <c r="H18" s="3" t="n">
         <v>0.408</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
-      <c r="L18" s="1"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="7"/>
-      <c r="D19" s="4"/>
+      <c r="D19" s="3"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4" t="n">
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="n">
         <v>0.395</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
-      <c r="L19" s="1"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="4"/>
+      <c r="D20" s="3"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4" t="n">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="n">
         <v>0.399</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
-      <c r="L20" s="1"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1"/>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="4"/>
+      <c r="D21" s="3"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4" t="n">
+      <c r="G21" s="3"/>
+      <c r="H21" s="3" t="n">
         <v>0.407</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
-      <c r="L21" s="1"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
       <c r="I22" s="13"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
-      <c r="L22" s="1"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1"/>
-      <c r="B23" s="3" t="s">
+      <c r="A23" s="2"/>
+      <c r="B23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
       <c r="I23" s="13"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1"/>
-      <c r="B24" s="15" t="s">
+      <c r="A24" s="2"/>
+      <c r="B24" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C24" s="5" t="e">
@@ -1818,49 +1863,49 @@
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="1"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1876,4 +1921,450 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B3:K25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="80.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4"/>
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="e">
+        <f aca="false">AVERAGE(C5:C9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D12" s="2" t="e">
+        <f aca="false">AVERAGE(D5:D9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E12" s="2" t="e">
+        <f aca="false">AVERAGE(E5:E9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F12" s="2" t="e">
+        <f aca="false">AVERAGE(F5:F9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="2" t="e">
+        <f aca="false">AVERAGE(G5:G9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H12" s="2" t="e">
+        <f aca="false">AVERAGE(H5:H9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I12" s="2" t="e">
+        <f aca="false">AVERAGE(I5:I9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J12" s="2" t="e">
+        <f aca="false">AVERAGE(J5:J9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="80.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4"/>
+      <c r="C17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="5"/>
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="40.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="13"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="13"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="27.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="5" t="e">
+        <f aca="false">AVERAGE(C18:C22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D25" s="5" t="e">
+        <f aca="false">AVERAGE(D18:D22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E25" s="5" t="e">
+        <f aca="false">AVERAGE(E18:E22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F25" s="5" t="e">
+        <f aca="false">AVERAGE(F18:F22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="5" t="e">
+        <f aca="false">AVERAGE(G18:G22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H25" s="5" t="e">
+        <f aca="false">AVERAGE(H18:H22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I25" s="5" t="e">
+        <f aca="false">AVERAGE(I18:I22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B16:K16"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>